--- a/flow-test.xlsx
+++ b/flow-test.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://luminotech-my.sharepoint.com/personal/rob_brennan-craddock_lumino-tech_co_uk/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobBrennan-Craddock\Documents\GitHub\Lumino\flow-trial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{139E86C3-0FA2-4E06-8FC9-B92CFF593783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BFD86AB-ACEB-4037-BBD3-FB0B32210D36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{7AD1DD7D-EE25-40D4-9390-5595088FEC5F}"/>
   </bookViews>
@@ -451,7 +451,7 @@
         <v>3</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -460,7 +460,7 @@
       </c>
       <c r="B7">
         <f>B4+B5+B6</f>
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/flow-test.xlsx
+++ b/flow-test.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobBrennan-Craddock\Documents\GitHub\Lumino\flow-trial\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://luminotech-my.sharepoint.com/personal/craig_grocott_lumino-tech_co_uk/Documents/Documents/GitHub/flow-trial/flow-trial/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BFD86AB-ACEB-4037-BBD3-FB0B32210D36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{5BFD86AB-ACEB-4037-BBD3-FB0B32210D36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34EA1470-5405-4025-A18B-034962F0A80F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{7AD1DD7D-EE25-40D4-9390-5595088FEC5F}"/>
+    <workbookView xWindow="40980" yWindow="-6615" windowWidth="25620" windowHeight="15600" xr2:uid="{7AD1DD7D-EE25-40D4-9390-5595088FEC5F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -423,14 +423,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D904D0D-C3CB-4C8B-948C-48401FD8107C}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -438,15 +438,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>2</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -454,13 +454,13 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
       <c r="B7">
         <f>B4+B5+B6</f>
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/flow-test.xlsx
+++ b/flow-test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://luminotech-my.sharepoint.com/personal/craig_grocott_lumino-tech_co_uk/Documents/Documents/GitHub/flow-trial/flow-trial/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{5BFD86AB-ACEB-4037-BBD3-FB0B32210D36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34EA1470-5405-4025-A18B-034962F0A80F}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{5BFD86AB-ACEB-4037-BBD3-FB0B32210D36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B21F7313-CC4C-49D4-89AB-8C655BC3198A}"/>
   <bookViews>
     <workbookView xWindow="40980" yWindow="-6615" windowWidth="25620" windowHeight="15600" xr2:uid="{7AD1DD7D-EE25-40D4-9390-5595088FEC5F}"/>
   </bookViews>
@@ -443,7 +443,7 @@
         <v>2</v>
       </c>
       <c r="B5">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -460,7 +460,7 @@
       </c>
       <c r="B7">
         <f>B4+B5+B6</f>
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
